--- a/Development/Data/TinkerLab_HIVCoding.xlsx
+++ b/Development/Data/TinkerLab_HIVCoding.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bfa5f505eae3b06d/ARBEIT/Frankfurt/Metadaten/HIV/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Basti\ARBEIT Lokal\TinkerLab\Development\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1609" documentId="13_ncr:1_{E7ED7552-0E3E-4EC5-9DB6-E60AF104923A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7B25475-F328-4BE6-9818-933886658074}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD77A6B-F4C7-482C-AA9F-35BC5E0F46E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7247F1A3-D9E4-424E-8D2F-B9781ECCC0FE}"/>
   </bookViews>
@@ -903,12 +903,6 @@
     <t>Plausible</t>
   </si>
   <si>
-    <t>HIVInformationClass</t>
-  </si>
-  <si>
-    <t>HIVInformationValue</t>
-  </si>
-  <si>
     <t>HIVCodingPlausibility</t>
   </si>
   <si>
@@ -918,18 +912,9 @@
     <t>HIVCondition</t>
   </si>
   <si>
-    <t>HIVConditionGerman</t>
-  </si>
-  <si>
-    <t>HIVDiseaseClass</t>
-  </si>
-  <si>
     <t>HIVDisease</t>
   </si>
   <si>
-    <t>HIVDiseaseGerman</t>
-  </si>
-  <si>
     <t>F02.4</t>
   </si>
   <si>
@@ -1051,6 +1036,21 @@
   </si>
   <si>
     <t>U85!</t>
+  </si>
+  <si>
+    <t>HIVCondition.German</t>
+  </si>
+  <si>
+    <t>HIVInformation.Class</t>
+  </si>
+  <si>
+    <t>HIVInformation.Value</t>
+  </si>
+  <si>
+    <t>HIVDisease.German</t>
+  </si>
+  <si>
+    <t>HIVDisease.Class</t>
   </si>
 </sst>
 </file>
@@ -1492,31 +1492,31 @@
         <v>82</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>291</v>
+        <v>331</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>83</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>289</v>
-      </c>
       <c r="I1" s="7" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -1530,7 +1530,7 @@
         <v>197</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>194</v>
@@ -1539,13 +1539,13 @@
         <v>285</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>278</v>
@@ -1569,14 +1569,14 @@
         <v>285</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I3" s="1" t="str">
         <f t="shared" ref="I3:I10" si="0">F3</f>
         <v>A</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -1593,7 +1593,7 @@
         <v>184</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>278</v>
@@ -1602,14 +1602,14 @@
         <v>285</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I4" s="1" t="str">
         <f t="shared" si="0"/>
         <v>A</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -1623,10 +1623,10 @@
         <v>176</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>278</v>
@@ -1635,14 +1635,14 @@
         <v>285</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I5" s="1" t="str">
         <f t="shared" ref="I5" si="1">F5</f>
         <v>A</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -1659,7 +1659,7 @@
         <v>186</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>279</v>
@@ -1668,13 +1668,13 @@
         <v>188</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -1688,10 +1688,10 @@
         <v>176</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>279</v>
@@ -1700,13 +1700,13 @@
         <v>188</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -1723,7 +1723,7 @@
         <v>187</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>280</v>
@@ -1732,13 +1732,13 @@
         <v>188</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -1752,10 +1752,10 @@
         <v>176</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>280</v>
@@ -1764,13 +1764,13 @@
         <v>188</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -1787,7 +1787,7 @@
         <v>192</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>278</v>
@@ -1796,14 +1796,14 @@
         <v>285</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>A</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -1817,10 +1817,10 @@
         <v>176</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>278</v>
@@ -1829,14 +1829,14 @@
         <v>285</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I11" s="1" t="str">
         <f t="shared" ref="I11" si="2">F11</f>
         <v>A</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -1862,7 +1862,7 @@
         <v>285</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>278</v>
@@ -1882,7 +1882,7 @@
         <v>176</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>284</v>
@@ -1894,7 +1894,7 @@
         <v>285</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>278</v>
@@ -1926,7 +1926,7 @@
         <v>285</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>278</v>
@@ -1946,7 +1946,7 @@
         <v>176</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>284</v>
@@ -1958,7 +1958,7 @@
         <v>285</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>278</v>
@@ -1990,7 +1990,7 @@
         <v>285</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>278</v>
@@ -2010,7 +2010,7 @@
         <v>176</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>284</v>
@@ -2022,7 +2022,7 @@
         <v>285</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>278</v>
@@ -2054,13 +2054,13 @@
         <v>285</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>278</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2074,7 +2074,7 @@
         <v>176</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>284</v>
@@ -2086,13 +2086,13 @@
         <v>285</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>278</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2115,13 +2115,13 @@
         <v>285</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>278</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2135,7 +2135,7 @@
         <v>176</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>277</v>
@@ -2144,13 +2144,13 @@
         <v>285</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>278</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>194</v>
@@ -2174,13 +2174,13 @@
         <v>285</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2197,7 +2197,7 @@
         <v>184</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>278</v>
@@ -2206,13 +2206,13 @@
         <v>188</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2226,10 +2226,10 @@
         <v>198</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>278</v>
@@ -2238,13 +2238,13 @@
         <v>188</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2261,7 +2261,7 @@
         <v>186</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>279</v>
@@ -2270,14 +2270,14 @@
         <v>285</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I25" s="1" t="str">
         <f t="shared" ref="I25:I139" si="3">F25</f>
         <v>B</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2291,10 +2291,10 @@
         <v>198</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>279</v>
@@ -2303,14 +2303,14 @@
         <v>285</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I26" s="1" t="str">
         <f t="shared" ref="I26" si="4">F26</f>
         <v>B</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2327,7 +2327,7 @@
         <v>187</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>280</v>
@@ -2343,7 +2343,7 @@
         <v>C</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2357,10 +2357,10 @@
         <v>198</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>280</v>
@@ -2376,7 +2376,7 @@
         <v>C</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2393,7 +2393,7 @@
         <v>192</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>194</v>
@@ -2402,13 +2402,13 @@
         <v>285</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2422,10 +2422,10 @@
         <v>198</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>194</v>
@@ -2434,13 +2434,13 @@
         <v>285</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2466,10 +2466,10 @@
         <v>285</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J31" s="1">
         <v>1</v>
@@ -2486,7 +2486,7 @@
         <v>198</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>284</v>
@@ -2498,10 +2498,10 @@
         <v>285</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J32" s="1">
         <v>1</v>
@@ -2530,10 +2530,10 @@
         <v>285</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J33" s="1">
         <v>2</v>
@@ -2550,7 +2550,7 @@
         <v>198</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>284</v>
@@ -2562,10 +2562,10 @@
         <v>285</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J34" s="1">
         <v>2</v>
@@ -2594,10 +2594,10 @@
         <v>285</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J35" s="1">
         <v>3</v>
@@ -2614,7 +2614,7 @@
         <v>198</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>284</v>
@@ -2626,10 +2626,10 @@
         <v>285</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J36" s="1">
         <v>3</v>
@@ -2658,13 +2658,13 @@
         <v>285</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2678,7 +2678,7 @@
         <v>198</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>284</v>
@@ -2690,13 +2690,13 @@
         <v>285</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2719,13 +2719,13 @@
         <v>285</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2739,7 +2739,7 @@
         <v>198</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>277</v>
@@ -2748,13 +2748,13 @@
         <v>285</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2768,7 +2768,7 @@
         <v>199</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>194</v>
@@ -2777,13 +2777,13 @@
         <v>285</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2800,7 +2800,7 @@
         <v>184</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>278</v>
@@ -2809,13 +2809,13 @@
         <v>188</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2829,10 +2829,10 @@
         <v>199</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>278</v>
@@ -2841,13 +2841,13 @@
         <v>188</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2864,7 +2864,7 @@
         <v>186</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>279</v>
@@ -2873,14 +2873,14 @@
         <v>285</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I44" s="1" t="str">
         <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2894,10 +2894,10 @@
         <v>199</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>279</v>
@@ -2906,14 +2906,14 @@
         <v>285</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I45" s="1" t="str">
         <f t="shared" ref="I45" si="6">F45</f>
         <v>B</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2930,7 +2930,7 @@
         <v>187</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>280</v>
@@ -2946,7 +2946,7 @@
         <v>C</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2960,10 +2960,10 @@
         <v>199</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>280</v>
@@ -2979,7 +2979,7 @@
         <v>C</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2996,7 +2996,7 @@
         <v>192</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>194</v>
@@ -3005,13 +3005,13 @@
         <v>285</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3025,10 +3025,10 @@
         <v>199</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>194</v>
@@ -3037,13 +3037,13 @@
         <v>285</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3069,10 +3069,10 @@
         <v>285</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J50" s="1">
         <v>1</v>
@@ -3089,7 +3089,7 @@
         <v>199</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>284</v>
@@ -3101,10 +3101,10 @@
         <v>285</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J51" s="1">
         <v>1</v>
@@ -3133,10 +3133,10 @@
         <v>285</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J52" s="1">
         <v>2</v>
@@ -3153,7 +3153,7 @@
         <v>199</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>284</v>
@@ -3165,10 +3165,10 @@
         <v>285</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J53" s="1">
         <v>2</v>
@@ -3197,10 +3197,10 @@
         <v>285</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J54" s="1">
         <v>3</v>
@@ -3217,7 +3217,7 @@
         <v>199</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>284</v>
@@ -3229,10 +3229,10 @@
         <v>285</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J55" s="1">
         <v>3</v>
@@ -3261,13 +3261,13 @@
         <v>285</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3281,7 +3281,7 @@
         <v>199</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>284</v>
@@ -3293,13 +3293,13 @@
         <v>285</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3322,13 +3322,13 @@
         <v>285</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3342,7 +3342,7 @@
         <v>199</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>277</v>
@@ -3351,13 +3351,13 @@
         <v>285</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3371,7 +3371,7 @@
         <v>28</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>194</v>
@@ -3380,13 +3380,13 @@
         <v>285</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3403,7 +3403,7 @@
         <v>184</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>278</v>
@@ -3412,13 +3412,13 @@
         <v>188</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3432,10 +3432,10 @@
         <v>28</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>278</v>
@@ -3444,13 +3444,13 @@
         <v>188</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3467,7 +3467,7 @@
         <v>186</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>279</v>
@@ -3476,14 +3476,14 @@
         <v>285</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I63" s="1" t="str">
         <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3497,10 +3497,10 @@
         <v>28</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>279</v>
@@ -3509,14 +3509,14 @@
         <v>285</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I64" s="1" t="str">
         <f t="shared" ref="I64" si="8">F64</f>
         <v>B</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3533,7 +3533,7 @@
         <v>187</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>280</v>
@@ -3549,7 +3549,7 @@
         <v>C</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3563,10 +3563,10 @@
         <v>28</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>280</v>
@@ -3582,7 +3582,7 @@
         <v>C</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3599,7 +3599,7 @@
         <v>192</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>194</v>
@@ -3608,13 +3608,13 @@
         <v>285</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3628,10 +3628,10 @@
         <v>28</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>194</v>
@@ -3640,13 +3640,13 @@
         <v>285</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3672,10 +3672,10 @@
         <v>285</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J69" s="1">
         <v>1</v>
@@ -3692,7 +3692,7 @@
         <v>28</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>284</v>
@@ -3704,10 +3704,10 @@
         <v>285</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J70" s="1">
         <v>1</v>
@@ -3736,10 +3736,10 @@
         <v>285</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J71" s="1">
         <v>2</v>
@@ -3756,7 +3756,7 @@
         <v>28</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>284</v>
@@ -3768,10 +3768,10 @@
         <v>285</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J72" s="1">
         <v>2</v>
@@ -3800,10 +3800,10 @@
         <v>285</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J73" s="1">
         <v>3</v>
@@ -3820,7 +3820,7 @@
         <v>28</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>284</v>
@@ -3832,10 +3832,10 @@
         <v>285</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J74" s="1">
         <v>3</v>
@@ -3864,13 +3864,13 @@
         <v>285</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3884,7 +3884,7 @@
         <v>28</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>284</v>
@@ -3896,13 +3896,13 @@
         <v>285</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3925,13 +3925,13 @@
         <v>285</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3945,7 +3945,7 @@
         <v>28</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>277</v>
@@ -3954,13 +3954,13 @@
         <v>285</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3974,7 +3974,7 @@
         <v>178</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>194</v>
@@ -3983,13 +3983,13 @@
         <v>285</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4006,7 +4006,7 @@
         <v>184</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>278</v>
@@ -4015,14 +4015,14 @@
         <v>285</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I80" s="1" t="str">
         <f t="shared" si="3"/>
         <v>A</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4036,10 +4036,10 @@
         <v>178</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>278</v>
@@ -4048,14 +4048,14 @@
         <v>285</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I81" s="1" t="str">
         <f t="shared" ref="I81" si="10">F81</f>
         <v>A</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4072,7 +4072,7 @@
         <v>186</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>279</v>
@@ -4081,14 +4081,14 @@
         <v>285</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I82" s="1" t="str">
         <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4102,10 +4102,10 @@
         <v>178</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>279</v>
@@ -4114,14 +4114,14 @@
         <v>285</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I83" s="1" t="str">
         <f t="shared" ref="I83" si="11">F83</f>
         <v>B</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4138,7 +4138,7 @@
         <v>187</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>280</v>
@@ -4154,7 +4154,7 @@
         <v>C</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4168,10 +4168,10 @@
         <v>178</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>280</v>
@@ -4187,7 +4187,7 @@
         <v>C</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4204,7 +4204,7 @@
         <v>192</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>194</v>
@@ -4213,13 +4213,13 @@
         <v>285</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4233,10 +4233,10 @@
         <v>178</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>194</v>
@@ -4245,13 +4245,13 @@
         <v>285</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4277,10 +4277,10 @@
         <v>285</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J88" s="1">
         <v>1</v>
@@ -4297,7 +4297,7 @@
         <v>178</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>284</v>
@@ -4309,10 +4309,10 @@
         <v>285</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J89" s="1">
         <v>1</v>
@@ -4341,10 +4341,10 @@
         <v>285</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J90" s="1">
         <v>2</v>
@@ -4361,7 +4361,7 @@
         <v>178</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>284</v>
@@ -4373,10 +4373,10 @@
         <v>285</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J91" s="1">
         <v>2</v>
@@ -4405,10 +4405,10 @@
         <v>285</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J92" s="1">
         <v>3</v>
@@ -4425,7 +4425,7 @@
         <v>178</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>284</v>
@@ -4437,10 +4437,10 @@
         <v>285</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J93" s="1">
         <v>3</v>
@@ -4469,13 +4469,13 @@
         <v>285</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4489,7 +4489,7 @@
         <v>178</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>284</v>
@@ -4501,13 +4501,13 @@
         <v>285</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4530,13 +4530,13 @@
         <v>285</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4550,7 +4550,7 @@
         <v>178</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>277</v>
@@ -4559,13 +4559,13 @@
         <v>285</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4579,7 +4579,7 @@
         <v>180</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>278</v>
@@ -4588,14 +4588,14 @@
         <v>285</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I98" s="1" t="str">
         <f t="shared" si="3"/>
         <v>A</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4612,7 +4612,7 @@
         <v>184</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>278</v>
@@ -4621,14 +4621,14 @@
         <v>285</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I99" s="1" t="str">
         <f t="shared" si="3"/>
         <v>A</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4642,10 +4642,10 @@
         <v>180</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>278</v>
@@ -4654,14 +4654,14 @@
         <v>285</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I100" s="1" t="str">
         <f t="shared" ref="I100" si="13">F100</f>
         <v>A</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4678,7 +4678,7 @@
         <v>186</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>279</v>
@@ -4687,13 +4687,13 @@
         <v>188</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4707,10 +4707,10 @@
         <v>180</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>279</v>
@@ -4719,13 +4719,13 @@
         <v>188</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4742,7 +4742,7 @@
         <v>187</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>280</v>
@@ -4751,13 +4751,13 @@
         <v>188</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4771,10 +4771,10 @@
         <v>180</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>280</v>
@@ -4783,13 +4783,13 @@
         <v>188</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4806,7 +4806,7 @@
         <v>192</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>194</v>
@@ -4815,13 +4815,13 @@
         <v>285</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>278</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4835,10 +4835,10 @@
         <v>180</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>194</v>
@@ -4847,13 +4847,13 @@
         <v>285</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>278</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -4879,7 +4879,7 @@
         <v>285</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>278</v>
@@ -4899,7 +4899,7 @@
         <v>180</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>284</v>
@@ -4911,7 +4911,7 @@
         <v>285</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>278</v>
@@ -4943,7 +4943,7 @@
         <v>285</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>278</v>
@@ -4963,7 +4963,7 @@
         <v>180</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>284</v>
@@ -4975,7 +4975,7 @@
         <v>285</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>278</v>
@@ -5007,7 +5007,7 @@
         <v>285</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>278</v>
@@ -5027,7 +5027,7 @@
         <v>180</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>284</v>
@@ -5039,7 +5039,7 @@
         <v>285</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>278</v>
@@ -5071,13 +5071,13 @@
         <v>285</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>278</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5091,7 +5091,7 @@
         <v>180</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>284</v>
@@ -5103,13 +5103,13 @@
         <v>285</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>278</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5132,13 +5132,13 @@
         <v>285</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>278</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5152,7 +5152,7 @@
         <v>180</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>277</v>
@@ -5161,13 +5161,13 @@
         <v>285</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>278</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5181,7 +5181,7 @@
         <v>179</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>194</v>
@@ -5190,13 +5190,13 @@
         <v>285</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5213,7 +5213,7 @@
         <v>184</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>278</v>
@@ -5222,14 +5222,14 @@
         <v>285</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I118" s="1" t="str">
         <f t="shared" si="3"/>
         <v>A</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5243,10 +5243,10 @@
         <v>179</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>278</v>
@@ -5255,14 +5255,14 @@
         <v>285</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I119" s="1" t="str">
         <f t="shared" ref="I119" si="14">F119</f>
         <v>A</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5279,7 +5279,7 @@
         <v>186</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>279</v>
@@ -5288,14 +5288,14 @@
         <v>285</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I120" s="1" t="str">
         <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5309,10 +5309,10 @@
         <v>179</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>279</v>
@@ -5321,14 +5321,14 @@
         <v>285</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I121" s="1" t="str">
         <f t="shared" ref="I121" si="15">F121</f>
         <v>B</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5345,7 +5345,7 @@
         <v>187</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>280</v>
@@ -5361,7 +5361,7 @@
         <v>C</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5375,10 +5375,10 @@
         <v>179</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>280</v>
@@ -5394,7 +5394,7 @@
         <v>C</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5411,7 +5411,7 @@
         <v>192</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>194</v>
@@ -5420,13 +5420,13 @@
         <v>285</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5440,10 +5440,10 @@
         <v>179</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>194</v>
@@ -5452,13 +5452,13 @@
         <v>285</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5484,10 +5484,10 @@
         <v>285</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J126" s="1">
         <v>1</v>
@@ -5504,7 +5504,7 @@
         <v>179</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>284</v>
@@ -5516,10 +5516,10 @@
         <v>285</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J127" s="1">
         <v>1</v>
@@ -5548,10 +5548,10 @@
         <v>285</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J128" s="1">
         <v>2</v>
@@ -5568,7 +5568,7 @@
         <v>179</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>284</v>
@@ -5580,10 +5580,10 @@
         <v>285</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J129" s="1">
         <v>2</v>
@@ -5612,10 +5612,10 @@
         <v>285</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J130" s="1">
         <v>3</v>
@@ -5632,7 +5632,7 @@
         <v>179</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>284</v>
@@ -5644,10 +5644,10 @@
         <v>285</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J131" s="1">
         <v>3</v>
@@ -5676,13 +5676,13 @@
         <v>285</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="133" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5696,7 +5696,7 @@
         <v>179</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>284</v>
@@ -5708,13 +5708,13 @@
         <v>285</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="134" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5737,13 +5737,13 @@
         <v>285</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5757,7 +5757,7 @@
         <v>179</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>277</v>
@@ -5766,13 +5766,13 @@
         <v>285</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5786,7 +5786,7 @@
         <v>274</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>194</v>
@@ -5795,13 +5795,13 @@
         <v>285</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5818,7 +5818,7 @@
         <v>184</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>278</v>
@@ -5827,13 +5827,13 @@
         <v>188</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="138" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5847,10 +5847,10 @@
         <v>274</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>278</v>
@@ -5859,13 +5859,13 @@
         <v>188</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="139" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5882,7 +5882,7 @@
         <v>186</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>279</v>
@@ -5891,14 +5891,14 @@
         <v>285</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I139" s="1" t="str">
         <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="140" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5912,10 +5912,10 @@
         <v>274</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>279</v>
@@ -5924,14 +5924,14 @@
         <v>285</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I140" s="1" t="str">
         <f t="shared" ref="I140" si="17">F140</f>
         <v>B</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5948,7 +5948,7 @@
         <v>187</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>280</v>
@@ -5964,7 +5964,7 @@
         <v>C</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="142" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5978,10 +5978,10 @@
         <v>274</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>280</v>
@@ -5997,7 +5997,7 @@
         <v>C</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="143" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6014,7 +6014,7 @@
         <v>192</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>194</v>
@@ -6023,13 +6023,13 @@
         <v>285</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="144" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6043,10 +6043,10 @@
         <v>274</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>194</v>
@@ -6055,13 +6055,13 @@
         <v>285</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6087,10 +6087,10 @@
         <v>285</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J145" s="1">
         <v>1</v>
@@ -6107,7 +6107,7 @@
         <v>274</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>284</v>
@@ -6119,10 +6119,10 @@
         <v>285</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J146" s="1">
         <v>1</v>
@@ -6151,10 +6151,10 @@
         <v>285</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J147" s="1">
         <v>2</v>
@@ -6171,7 +6171,7 @@
         <v>274</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>284</v>
@@ -6183,10 +6183,10 @@
         <v>285</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J148" s="1">
         <v>2</v>
@@ -6215,10 +6215,10 @@
         <v>285</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J149" s="1">
         <v>3</v>
@@ -6235,7 +6235,7 @@
         <v>274</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>284</v>
@@ -6247,10 +6247,10 @@
         <v>285</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J150" s="1">
         <v>3</v>
@@ -6279,13 +6279,13 @@
         <v>285</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6299,7 +6299,7 @@
         <v>274</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>284</v>
@@ -6311,13 +6311,13 @@
         <v>285</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6340,13 +6340,13 @@
         <v>285</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="154" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6360,7 +6360,7 @@
         <v>274</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>277</v>
@@ -6369,13 +6369,13 @@
         <v>285</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -6411,16 +6411,16 @@
         <v>121</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>292</v>
+        <v>335</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>294</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6431,10 +6431,10 @@
         <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>80</v>
@@ -6451,10 +6451,10 @@
         <v>172</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>181</v>
@@ -6471,10 +6471,10 @@
         <v>174</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>182</v>
@@ -6492,10 +6492,10 @@
         <v>195</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>196</v>
@@ -6509,22 +6509,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6532,22 +6532,22 @@
         <v>125</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>125</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6555,22 +6555,22 @@
         <v>125</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>125</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6578,22 +6578,22 @@
         <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6601,22 +6601,22 @@
         <v>174</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>174</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6624,22 +6624,22 @@
         <v>185</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>185</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6647,22 +6647,22 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6670,22 +6670,22 @@
         <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6693,22 +6693,22 @@
         <v>27</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6716,22 +6716,22 @@
         <v>5</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6739,22 +6739,22 @@
         <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>319</v>
-      </c>
       <c r="G16" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6762,22 +6762,22 @@
         <v>174</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>174</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>319</v>
-      </c>
       <c r="G17" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6785,22 +6785,22 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>319</v>
-      </c>
       <c r="G18" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6808,7 +6808,7 @@
         <v>203</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>162</v>
@@ -6825,7 +6825,7 @@
         <v>204</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>162</v>
@@ -6842,7 +6842,7 @@
         <v>207</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>162</v>
@@ -6859,7 +6859,7 @@
         <v>208</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>162</v>
@@ -6876,7 +6876,7 @@
         <v>209</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>162</v>
@@ -6893,7 +6893,7 @@
         <v>210</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>162</v>
@@ -6910,7 +6910,7 @@
         <v>211</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>162</v>
@@ -6927,7 +6927,7 @@
         <v>213</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>162</v>
@@ -6944,7 +6944,7 @@
         <v>214</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>162</v>
@@ -6961,7 +6961,7 @@
         <v>215</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>162</v>
@@ -6978,7 +6978,7 @@
         <v>216</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>162</v>
@@ -6995,7 +6995,7 @@
         <v>217</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>162</v>
@@ -7012,7 +7012,7 @@
         <v>218</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>162</v>
@@ -7029,7 +7029,7 @@
         <v>219</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>162</v>
@@ -7046,7 +7046,7 @@
         <v>220</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>162</v>
@@ -7063,7 +7063,7 @@
         <v>221</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>162</v>
@@ -7080,7 +7080,7 @@
         <v>222</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>162</v>
@@ -7097,7 +7097,7 @@
         <v>223</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>162</v>
@@ -7114,7 +7114,7 @@
         <v>224</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>162</v>
@@ -7131,7 +7131,7 @@
         <v>225</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>162</v>
@@ -7148,7 +7148,7 @@
         <v>226</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>162</v>
@@ -7165,7 +7165,7 @@
         <v>227</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>162</v>
@@ -7182,7 +7182,7 @@
         <v>228</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>162</v>
@@ -7199,7 +7199,7 @@
         <v>229</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>162</v>
@@ -7216,7 +7216,7 @@
         <v>230</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>162</v>
@@ -7233,7 +7233,7 @@
         <v>231</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>162</v>
@@ -7250,7 +7250,7 @@
         <v>232</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>162</v>
@@ -7267,7 +7267,7 @@
         <v>233</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>162</v>
@@ -7284,7 +7284,7 @@
         <v>234</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>162</v>
@@ -7301,7 +7301,7 @@
         <v>235</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>162</v>
@@ -7318,7 +7318,7 @@
         <v>236</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>162</v>
@@ -7335,7 +7335,7 @@
         <v>237</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>162</v>
@@ -7352,7 +7352,7 @@
         <v>238</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>162</v>
@@ -7369,7 +7369,7 @@
         <v>239</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>162</v>
@@ -7386,7 +7386,7 @@
         <v>240</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>162</v>
@@ -7403,7 +7403,7 @@
         <v>241</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>162</v>
@@ -7420,7 +7420,7 @@
         <v>242</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>162</v>
@@ -7437,7 +7437,7 @@
         <v>243</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>162</v>
@@ -7454,7 +7454,7 @@
         <v>244</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>162</v>
@@ -7471,7 +7471,7 @@
         <v>245</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>162</v>
@@ -7488,7 +7488,7 @@
         <v>246</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>162</v>
@@ -7505,7 +7505,7 @@
         <v>247</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>162</v>
@@ -7522,7 +7522,7 @@
         <v>248</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>162</v>
@@ -7541,7 +7541,7 @@
       <c r="B62" s="4"/>
       <c r="C62" s="5"/>
       <c r="D62" s="4" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>162</v>
@@ -7561,7 +7561,7 @@
         <v>125</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>162</v>
@@ -7584,7 +7584,7 @@
         <v>5</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>161</v>
@@ -7607,7 +7607,7 @@
         <v>5</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>161</v>
@@ -7630,7 +7630,7 @@
         <v>5</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>161</v>
@@ -7650,7 +7650,7 @@
         <v>5</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>161</v>
@@ -7673,7 +7673,7 @@
         <v>5</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>161</v>
@@ -7696,7 +7696,7 @@
         <v>5</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>161</v>
@@ -7719,7 +7719,7 @@
         <v>5</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>161</v>
@@ -7739,7 +7739,7 @@
         <v>5</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>161</v>
@@ -7762,7 +7762,7 @@
         <v>5</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>161</v>
@@ -7785,7 +7785,7 @@
         <v>5</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>161</v>
@@ -7802,22 +7802,22 @@
         <v>27</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -7825,22 +7825,22 @@
         <v>27</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -7854,7 +7854,7 @@
         <v>5</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>161</v>
@@ -7877,7 +7877,7 @@
         <v>5</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>161</v>
@@ -7900,7 +7900,7 @@
         <v>5</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>161</v>
@@ -7920,7 +7920,7 @@
         <v>5</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>161</v>
@@ -7940,7 +7940,7 @@
         <v>27</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>161</v>
@@ -7957,13 +7957,13 @@
         <v>5</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>161</v>
@@ -7983,10 +7983,10 @@
         <v>27</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>67</v>
@@ -8000,16 +8000,16 @@
         <v>5</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>67</v>
@@ -8023,16 +8023,16 @@
         <v>27</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>67</v>
@@ -8049,7 +8049,7 @@
         <v>5</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>161</v>
@@ -8069,7 +8069,7 @@
         <v>125</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>162</v>
@@ -8089,7 +8089,7 @@
         <v>125</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>162</v>
@@ -8109,7 +8109,7 @@
         <v>125</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>162</v>
@@ -8129,7 +8129,7 @@
         <v>125</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>162</v>
@@ -8149,7 +8149,7 @@
         <v>125</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>162</v>
@@ -8169,7 +8169,7 @@
         <v>125</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>162</v>
@@ -8189,7 +8189,7 @@
         <v>125</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>162</v>
@@ -8209,7 +8209,7 @@
         <v>125</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>162</v>
@@ -8229,7 +8229,7 @@
         <v>5</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>161</v>
@@ -8249,7 +8249,7 @@
         <v>5</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>161</v>
@@ -8269,7 +8269,7 @@
         <v>5</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>161</v>
@@ -8289,7 +8289,7 @@
         <v>5</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>161</v>
@@ -8309,7 +8309,7 @@
         <v>5</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>161</v>
@@ -8329,7 +8329,7 @@
         <v>5</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>161</v>
@@ -8349,7 +8349,7 @@
         <v>5</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>161</v>
@@ -8369,7 +8369,7 @@
         <v>5</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>161</v>
@@ -8389,7 +8389,7 @@
         <v>5</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>161</v>
@@ -8409,7 +8409,7 @@
         <v>5</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>161</v>
@@ -8429,7 +8429,7 @@
         <v>5</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>161</v>
@@ -8449,7 +8449,7 @@
         <v>125</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>162</v>
@@ -8469,7 +8469,7 @@
         <v>125</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>162</v>
@@ -8489,7 +8489,7 @@
         <v>125</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>162</v>
@@ -8509,7 +8509,7 @@
         <v>125</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>162</v>
@@ -8529,7 +8529,7 @@
         <v>125</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>162</v>
@@ -8549,7 +8549,7 @@
         <v>125</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>162</v>
@@ -8569,7 +8569,7 @@
         <v>125</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>162</v>
@@ -8589,7 +8589,7 @@
         <v>5</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>161</v>
@@ -8609,7 +8609,7 @@
         <v>5</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>161</v>
@@ -8629,7 +8629,7 @@
         <v>5</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>161</v>
@@ -8649,7 +8649,7 @@
         <v>5</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>161</v>
@@ -8669,7 +8669,7 @@
         <v>5</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>161</v>
@@ -8689,7 +8689,7 @@
         <v>5</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>161</v>
@@ -8709,7 +8709,7 @@
         <v>5</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>161</v>
@@ -8729,7 +8729,7 @@
         <v>5</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>161</v>
@@ -8749,7 +8749,7 @@
         <v>5</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>161</v>
@@ -8769,7 +8769,7 @@
         <v>5</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>161</v>
@@ -8789,7 +8789,7 @@
         <v>5</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>161</v>
@@ -8809,7 +8809,7 @@
         <v>5</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>161</v>
@@ -8829,7 +8829,7 @@
         <v>5</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>161</v>
@@ -8850,7 +8850,7 @@
         <v>5</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>161</v>
@@ -8871,7 +8871,7 @@
         <v>5</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>161</v>
@@ -8892,7 +8892,7 @@
         <v>5</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>161</v>
@@ -8913,7 +8913,7 @@
         <v>5</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>161</v>
@@ -8934,7 +8934,7 @@
         <v>5</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>161</v>
@@ -8955,7 +8955,7 @@
         <v>5</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>161</v>
@@ -8976,7 +8976,7 @@
         <v>5</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>161</v>
@@ -8997,7 +8997,7 @@
         <v>5</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>161</v>
@@ -9018,7 +9018,7 @@
         <v>5</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>161</v>
@@ -9039,7 +9039,7 @@
         <v>5</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>161</v>
@@ -9059,7 +9059,7 @@
         <v>5</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>161</v>
@@ -9079,7 +9079,7 @@
         <v>5</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>161</v>
@@ -9099,7 +9099,7 @@
         <v>5</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>161</v>
@@ -9119,7 +9119,7 @@
         <v>5</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>161</v>
@@ -9139,7 +9139,7 @@
         <v>5</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>161</v>
@@ -9159,7 +9159,7 @@
         <v>5</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>161</v>
@@ -9179,7 +9179,7 @@
         <v>5</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>161</v>
@@ -9199,7 +9199,7 @@
         <v>5</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>161</v>
@@ -9219,7 +9219,7 @@
         <v>5</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>161</v>
@@ -9239,7 +9239,7 @@
         <v>5</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>161</v>
@@ -9259,7 +9259,7 @@
         <v>5</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>161</v>
@@ -9279,7 +9279,7 @@
         <v>5</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>161</v>
@@ -9299,7 +9299,7 @@
         <v>5</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>161</v>
@@ -9319,7 +9319,7 @@
         <v>5</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>161</v>
@@ -9339,7 +9339,7 @@
         <v>5</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>161</v>
@@ -9359,7 +9359,7 @@
         <v>5</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>161</v>
@@ -9379,7 +9379,7 @@
         <v>5</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>161</v>
@@ -9399,7 +9399,7 @@
         <v>5</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>161</v>
@@ -9419,7 +9419,7 @@
         <v>5</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>161</v>
@@ -9439,7 +9439,7 @@
         <v>5</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>161</v>
@@ -9459,7 +9459,7 @@
         <v>5</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>161</v>
@@ -9479,7 +9479,7 @@
         <v>5</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>161</v>
@@ -9499,7 +9499,7 @@
         <v>5</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>161</v>
@@ -9519,7 +9519,7 @@
         <v>5</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>161</v>
@@ -9539,7 +9539,7 @@
         <v>5</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>161</v>
@@ -9559,7 +9559,7 @@
         <v>5</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>161</v>
@@ -9579,7 +9579,7 @@
         <v>5</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>161</v>
@@ -9599,7 +9599,7 @@
         <v>5</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>161</v>
@@ -9619,7 +9619,7 @@
         <v>5</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>161</v>
@@ -9639,7 +9639,7 @@
         <v>5</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>161</v>
@@ -9659,7 +9659,7 @@
         <v>5</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>161</v>
@@ -9679,7 +9679,7 @@
         <v>125</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>162</v>
@@ -9699,7 +9699,7 @@
         <v>125</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>162</v>
@@ -9719,7 +9719,7 @@
         <v>125</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>162</v>
@@ -9739,7 +9739,7 @@
         <v>125</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>162</v>
@@ -9759,7 +9759,7 @@
         <v>125</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>162</v>

--- a/Development/Data/TinkerLab_HIVCoding.xlsx
+++ b/Development/Data/TinkerLab_HIVCoding.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Basti\ARBEIT Lokal\TinkerLab\Development\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD77A6B-F4C7-482C-AA9F-35BC5E0F46E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C7B9C6-54A3-46BC-9939-0CA3C6CD79DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7247F1A3-D9E4-424E-8D2F-B9781ECCC0FE}"/>
+    <workbookView xWindow="0" yWindow="120" windowWidth="23040" windowHeight="12120" xr2:uid="{7247F1A3-D9E4-424E-8D2F-B9781ECCC0FE}"/>
   </bookViews>
   <sheets>
     <sheet name="HIVStatus" sheetId="2" r:id="rId1"/>
@@ -291,12 +291,6 @@
     <t>Invasive cervical cancer</t>
   </si>
   <si>
-    <t>PrimaryICDCode</t>
-  </si>
-  <si>
-    <t>SecondaryICDCode</t>
-  </si>
-  <si>
     <t>B37.1</t>
   </si>
   <si>
@@ -1041,16 +1035,22 @@
     <t>HIVCondition.German</t>
   </si>
   <si>
-    <t>HIVInformation.Class</t>
-  </si>
-  <si>
-    <t>HIVInformation.Value</t>
-  </si>
-  <si>
     <t>HIVDisease.German</t>
   </si>
   <si>
-    <t>HIVDisease.Class</t>
+    <t>PrimaryICD10Code</t>
+  </si>
+  <si>
+    <t>SecondaryICD10Code</t>
+  </si>
+  <si>
+    <t>HIVDiseaseClass</t>
+  </si>
+  <si>
+    <t>HIVInformationClass</t>
+  </si>
+  <si>
+    <t>HIVInformationValue</t>
   </si>
 </sst>
 </file>
@@ -1489,383 +1489,383 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I3" s="1" t="str">
         <f t="shared" ref="I3:I10" si="0">F3</f>
         <v>A</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I4" s="1" t="str">
         <f t="shared" si="0"/>
         <v>A</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I5" s="1" t="str">
         <f t="shared" ref="I5" si="1">F5</f>
         <v>A</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="H6" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C9" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>A</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C11" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I11" s="1" t="str">
         <f t="shared" ref="I11" si="2">F11</f>
         <v>A</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J12" s="1">
         <v>1</v>
@@ -1873,31 +1873,31 @@
     </row>
     <row r="13" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
@@ -1905,31 +1905,31 @@
     </row>
     <row r="14" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J14" s="1">
         <v>2</v>
@@ -1937,31 +1937,31 @@
     </row>
     <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J15" s="1">
         <v>2</v>
@@ -1969,31 +1969,31 @@
     </row>
     <row r="16" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C16" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J16" s="1">
         <v>3</v>
@@ -2001,31 +2001,31 @@
     </row>
     <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C17" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J17" s="1">
         <v>3</v>
@@ -2033,124 +2033,124 @@
     </row>
     <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C19" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="J20" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="C21" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2158,29 +2158,29 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2188,31 +2188,31 @@
         <v>5</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2220,31 +2220,31 @@
         <v>5</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2252,32 +2252,32 @@
         <v>5</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I25" s="1" t="str">
         <f t="shared" ref="I25:I139" si="3">F25</f>
         <v>B</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2285,32 +2285,32 @@
         <v>5</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I26" s="1" t="str">
         <f t="shared" ref="I26" si="4">F26</f>
         <v>B</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2318,32 +2318,32 @@
         <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I27" s="1" t="str">
         <f t="shared" si="3"/>
         <v>C</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2351,32 +2351,32 @@
         <v>5</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I28" s="1" t="str">
         <f t="shared" ref="I28" si="5">F28</f>
         <v>C</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2384,31 +2384,31 @@
         <v>5</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="G29" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2416,31 +2416,31 @@
         <v>5</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2448,28 +2448,28 @@
         <v>5</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J31" s="1">
         <v>1</v>
@@ -2480,28 +2480,28 @@
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J32" s="1">
         <v>1</v>
@@ -2512,28 +2512,28 @@
         <v>5</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J33" s="1">
         <v>2</v>
@@ -2544,28 +2544,28 @@
         <v>5</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J34" s="1">
         <v>2</v>
@@ -2576,28 +2576,28 @@
         <v>5</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J35" s="1">
         <v>3</v>
@@ -2608,28 +2608,28 @@
         <v>5</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J36" s="1">
         <v>3</v>
@@ -2640,31 +2640,31 @@
         <v>5</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2672,31 +2672,31 @@
         <v>5</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2704,28 +2704,28 @@
         <v>5</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2733,346 +2733,346 @@
         <v>5</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I44" s="1" t="str">
         <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I45" s="1" t="str">
         <f t="shared" ref="I45" si="6">F45</f>
         <v>B</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I46" s="1" t="str">
         <f t="shared" si="3"/>
         <v>C</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I47" s="1" t="str">
         <f t="shared" ref="I47" si="7">F47</f>
         <v>C</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="G48" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J50" s="1">
         <v>1</v>
@@ -3080,31 +3080,31 @@
     </row>
     <row r="51" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J51" s="1">
         <v>1</v>
@@ -3112,31 +3112,31 @@
     </row>
     <row r="52" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J52" s="1">
         <v>2</v>
@@ -3144,31 +3144,31 @@
     </row>
     <row r="53" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J53" s="1">
         <v>2</v>
@@ -3176,31 +3176,31 @@
     </row>
     <row r="54" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J54" s="1">
         <v>3</v>
@@ -3208,31 +3208,31 @@
     </row>
     <row r="55" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J55" s="1">
         <v>3</v>
@@ -3240,124 +3240,124 @@
     </row>
     <row r="56" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3365,28 +3365,28 @@
         <v>27</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3394,31 +3394,31 @@
         <v>27</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3426,31 +3426,31 @@
         <v>27</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3458,32 +3458,32 @@
         <v>27</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I63" s="1" t="str">
         <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3491,32 +3491,32 @@
         <v>27</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I64" s="1" t="str">
         <f t="shared" ref="I64" si="8">F64</f>
         <v>B</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3524,32 +3524,32 @@
         <v>27</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I65" s="1" t="str">
         <f t="shared" si="3"/>
         <v>C</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3557,32 +3557,32 @@
         <v>27</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I66" s="1" t="str">
         <f t="shared" ref="I66" si="9">F66</f>
         <v>C</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3590,31 +3590,31 @@
         <v>27</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D67" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="G67" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3622,31 +3622,31 @@
         <v>27</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3654,28 +3654,28 @@
         <v>27</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J69" s="1">
         <v>1</v>
@@ -3686,28 +3686,28 @@
         <v>27</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J70" s="1">
         <v>1</v>
@@ -3718,28 +3718,28 @@
         <v>27</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J71" s="1">
         <v>2</v>
@@ -3750,28 +3750,28 @@
         <v>27</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J72" s="1">
         <v>2</v>
@@ -3782,28 +3782,28 @@
         <v>27</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J73" s="1">
         <v>3</v>
@@ -3814,28 +3814,28 @@
         <v>27</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J74" s="1">
         <v>3</v>
@@ -3846,31 +3846,31 @@
         <v>27</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3878,31 +3878,31 @@
         <v>27</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3910,28 +3910,28 @@
         <v>27</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3939,348 +3939,348 @@
         <v>27</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I80" s="1" t="str">
         <f t="shared" si="3"/>
         <v>A</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I81" s="1" t="str">
         <f t="shared" ref="I81" si="10">F81</f>
         <v>A</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I82" s="1" t="str">
         <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I83" s="1" t="str">
         <f t="shared" ref="I83" si="11">F83</f>
         <v>B</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I84" s="1" t="str">
         <f t="shared" si="3"/>
         <v>C</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I85" s="1" t="str">
         <f t="shared" ref="I85" si="12">F85</f>
         <v>C</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D86" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="G86" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J88" s="1">
         <v>1</v>
@@ -4288,31 +4288,31 @@
     </row>
     <row r="89" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J89" s="1">
         <v>1</v>
@@ -4320,31 +4320,31 @@
     </row>
     <row r="90" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J90" s="1">
         <v>2</v>
@@ -4352,31 +4352,31 @@
     </row>
     <row r="91" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J91" s="1">
         <v>2</v>
@@ -4384,31 +4384,31 @@
     </row>
     <row r="92" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J92" s="1">
         <v>3</v>
@@ -4416,31 +4416,31 @@
     </row>
     <row r="93" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J93" s="1">
         <v>3</v>
@@ -4448,441 +4448,441 @@
     </row>
     <row r="94" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I98" s="1" t="str">
         <f t="shared" si="3"/>
         <v>A</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I99" s="1" t="str">
         <f t="shared" si="3"/>
         <v>A</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I100" s="1" t="str">
         <f t="shared" ref="I100" si="13">F100</f>
         <v>A</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D101" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G101" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="H101" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D105" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F105" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="G105" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J107" s="1">
         <v>1</v>
@@ -4890,31 +4890,31 @@
     </row>
     <row r="108" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J108" s="1">
         <v>1</v>
@@ -4922,31 +4922,31 @@
     </row>
     <row r="109" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J109" s="1">
         <v>2</v>
@@ -4954,31 +4954,31 @@
     </row>
     <row r="110" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J110" s="1">
         <v>2</v>
@@ -4986,31 +4986,31 @@
     </row>
     <row r="111" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J111" s="1">
         <v>3</v>
@@ -5018,31 +5018,31 @@
     </row>
     <row r="112" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J112" s="1">
         <v>3</v>
@@ -5050,444 +5050,444 @@
     </row>
     <row r="113" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D115" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="I115" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="F115" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="J115" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B118" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I118" s="1" t="str">
         <f t="shared" si="3"/>
         <v>A</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I119" s="1" t="str">
         <f t="shared" ref="I119" si="14">F119</f>
         <v>A</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I120" s="1" t="str">
         <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I121" s="1" t="str">
         <f t="shared" ref="I121" si="15">F121</f>
         <v>B</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I122" s="1" t="str">
         <f t="shared" si="3"/>
         <v>C</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I123" s="1" t="str">
         <f t="shared" ref="I123" si="16">F123</f>
         <v>C</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D124" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F124" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E124" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="G124" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J126" s="1">
         <v>1</v>
@@ -5495,31 +5495,31 @@
     </row>
     <row r="127" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J127" s="1">
         <v>1</v>
@@ -5527,31 +5527,31 @@
     </row>
     <row r="128" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J128" s="1">
         <v>2</v>
@@ -5559,31 +5559,31 @@
     </row>
     <row r="129" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J129" s="1">
         <v>2</v>
@@ -5591,31 +5591,31 @@
     </row>
     <row r="130" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J130" s="1">
         <v>3</v>
@@ -5623,31 +5623,31 @@
     </row>
     <row r="131" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J131" s="1">
         <v>3</v>
@@ -5655,442 +5655,442 @@
     </row>
     <row r="132" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="133" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="134" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="138" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="139" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I139" s="1" t="str">
         <f t="shared" si="3"/>
         <v>B</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="140" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I140" s="1" t="str">
         <f t="shared" ref="I140" si="17">F140</f>
         <v>B</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="E141" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I141" s="1" t="str">
         <f t="shared" ref="I141" si="18">F141</f>
         <v>C</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="142" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I142" s="1" t="str">
         <f t="shared" ref="I142" si="19">F142</f>
         <v>C</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="143" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D143" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F143" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E143" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="G143" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="144" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J145" s="1">
         <v>1</v>
@@ -6098,31 +6098,31 @@
     </row>
     <row r="146" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J146" s="1">
         <v>1</v>
@@ -6130,31 +6130,31 @@
     </row>
     <row r="147" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J147" s="1">
         <v>2</v>
@@ -6162,31 +6162,31 @@
     </row>
     <row r="148" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J148" s="1">
         <v>2</v>
@@ -6194,31 +6194,31 @@
     </row>
     <row r="149" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J149" s="1">
         <v>3</v>
@@ -6226,31 +6226,31 @@
     </row>
     <row r="150" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J150" s="1">
         <v>3</v>
@@ -6258,124 +6258,124 @@
     </row>
     <row r="151" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B151" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C151" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="E151" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C153" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D153" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="F153" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="154" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -6402,25 +6402,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6431,10 +6431,10 @@
         <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>80</v>
@@ -6445,63 +6445,63 @@
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6509,68 +6509,68 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>310</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6578,68 +6578,68 @@
         <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6647,22 +6647,22 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>311</v>
-      </c>
       <c r="G12" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6670,22 +6670,22 @@
         <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6693,22 +6693,22 @@
         <v>27</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6716,22 +6716,22 @@
         <v>5</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6739,45 +6739,45 @@
         <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -6785,772 +6785,772 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="5"/>
       <c r="D62" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -7558,16 +7558,16 @@
         <v>23</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>1</v>
@@ -7575,19 +7575,19 @@
     </row>
     <row r="64" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>54</v>
@@ -7598,19 +7598,19 @@
     </row>
     <row r="65" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>57</v>
@@ -7621,19 +7621,19 @@
     </row>
     <row r="66" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>55</v>
@@ -7644,16 +7644,16 @@
     </row>
     <row r="67" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>61</v>
@@ -7664,19 +7664,19 @@
     </row>
     <row r="68" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>58</v>
@@ -7690,16 +7690,16 @@
         <v>7</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>63</v>
@@ -7713,16 +7713,16 @@
         <v>7</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>63</v>
@@ -7739,10 +7739,10 @@
         <v>5</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>64</v>
@@ -7756,16 +7756,16 @@
         <v>4</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>64</v>
@@ -7779,16 +7779,16 @@
         <v>8</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>56</v>
@@ -7802,22 +7802,22 @@
         <v>27</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -7825,39 +7825,39 @@
         <v>27</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>59</v>
@@ -7868,19 +7868,19 @@
     </row>
     <row r="77" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>60</v>
@@ -7891,19 +7891,19 @@
     </row>
     <row r="78" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>62</v>
@@ -7914,16 +7914,16 @@
     </row>
     <row r="79" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>65</v>
@@ -7934,16 +7934,16 @@
     </row>
     <row r="80" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>66</v>
@@ -7957,16 +7957,16 @@
         <v>5</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>66</v>
@@ -7977,16 +7977,16 @@
     </row>
     <row r="82" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>67</v>
@@ -8000,16 +8000,16 @@
         <v>5</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>67</v>
@@ -8023,16 +8023,16 @@
         <v>27</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>67</v>
@@ -8049,10 +8049,10 @@
         <v>5</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>41</v>
@@ -8066,13 +8066,13 @@
         <v>22</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>68</v>
@@ -8083,16 +8083,16 @@
     </row>
     <row r="87" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>68</v>
@@ -8103,16 +8103,16 @@
     </row>
     <row r="88" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>68</v>
@@ -8123,16 +8123,16 @@
     </row>
     <row r="89" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>68</v>
@@ -8143,16 +8143,16 @@
     </row>
     <row r="90" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>68</v>
@@ -8163,16 +8163,16 @@
     </row>
     <row r="91" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>68</v>
@@ -8183,16 +8183,16 @@
     </row>
     <row r="92" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>68</v>
@@ -8203,16 +8203,16 @@
     </row>
     <row r="93" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>68</v>
@@ -8223,16 +8223,16 @@
     </row>
     <row r="94" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>69</v>
@@ -8249,10 +8249,10 @@
         <v>5</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>69</v>
@@ -8263,16 +8263,16 @@
     </row>
     <row r="96" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>69</v>
@@ -8283,16 +8283,16 @@
     </row>
     <row r="97" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>69</v>
@@ -8309,10 +8309,10 @@
         <v>5</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>70</v>
@@ -8329,10 +8329,10 @@
         <v>5</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>70</v>
@@ -8349,10 +8349,10 @@
         <v>5</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>70</v>
@@ -8369,10 +8369,10 @@
         <v>5</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>70</v>
@@ -8389,10 +8389,10 @@
         <v>5</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>70</v>
@@ -8409,10 +8409,10 @@
         <v>5</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>70</v>
@@ -8429,10 +8429,10 @@
         <v>5</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>71</v>
@@ -8446,13 +8446,13 @@
         <v>24</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>72</v>
@@ -8466,13 +8466,13 @@
         <v>25</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>72</v>
@@ -8483,116 +8483,116 @@
     </row>
     <row r="107" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>73</v>
@@ -8603,16 +8603,16 @@
     </row>
     <row r="113" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>73</v>
@@ -8623,16 +8623,16 @@
     </row>
     <row r="114" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>73</v>
@@ -8643,16 +8643,16 @@
     </row>
     <row r="115" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>74</v>
@@ -8663,16 +8663,16 @@
     </row>
     <row r="116" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>74</v>
@@ -8683,16 +8683,16 @@
     </row>
     <row r="117" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>74</v>
@@ -8703,16 +8703,16 @@
     </row>
     <row r="118" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>75</v>
@@ -8723,16 +8723,16 @@
     </row>
     <row r="119" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>75</v>
@@ -8749,10 +8749,10 @@
         <v>5</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>76</v>
@@ -8769,10 +8769,10 @@
         <v>5</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>77</v>
@@ -8789,10 +8789,10 @@
         <v>5</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>78</v>
@@ -8803,16 +8803,16 @@
     </row>
     <row r="123" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>78</v>
@@ -8829,10 +8829,10 @@
         <v>5</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>79</v>
@@ -8850,10 +8850,10 @@
         <v>5</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>79</v>
@@ -8871,10 +8871,10 @@
         <v>5</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>79</v>
@@ -8892,10 +8892,10 @@
         <v>5</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>79</v>
@@ -8913,10 +8913,10 @@
         <v>5</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>79</v>
@@ -8934,10 +8934,10 @@
         <v>5</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>79</v>
@@ -8955,10 +8955,10 @@
         <v>5</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>79</v>
@@ -8976,10 +8976,10 @@
         <v>5</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>79</v>
@@ -8997,10 +8997,10 @@
         <v>5</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>79</v>
@@ -9018,10 +9018,10 @@
         <v>5</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>79</v>
@@ -9039,10 +9039,10 @@
         <v>5</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>79</v>
@@ -9053,16 +9053,16 @@
     </row>
     <row r="135" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>79</v>
@@ -9073,16 +9073,16 @@
     </row>
     <row r="136" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>79</v>
@@ -9093,16 +9093,16 @@
     </row>
     <row r="137" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>79</v>
@@ -9113,16 +9113,16 @@
     </row>
     <row r="138" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>79</v>
@@ -9133,16 +9133,16 @@
     </row>
     <row r="139" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>79</v>
@@ -9153,16 +9153,16 @@
     </row>
     <row r="140" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>79</v>
@@ -9173,16 +9173,16 @@
     </row>
     <row r="141" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>79</v>
@@ -9193,16 +9193,16 @@
     </row>
     <row r="142" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>79</v>
@@ -9213,16 +9213,16 @@
     </row>
     <row r="143" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>79</v>
@@ -9233,16 +9233,16 @@
     </row>
     <row r="144" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>79</v>
@@ -9253,16 +9253,16 @@
     </row>
     <row r="145" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>79</v>
@@ -9273,16 +9273,16 @@
     </row>
     <row r="146" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>79</v>
@@ -9293,16 +9293,16 @@
     </row>
     <row r="147" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>79</v>
@@ -9313,16 +9313,16 @@
     </row>
     <row r="148" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>79</v>
@@ -9333,16 +9333,16 @@
     </row>
     <row r="149" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>79</v>
@@ -9353,16 +9353,16 @@
     </row>
     <row r="150" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>79</v>
@@ -9373,16 +9373,16 @@
     </row>
     <row r="151" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>79</v>
@@ -9393,16 +9393,16 @@
     </row>
     <row r="152" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>79</v>
@@ -9413,16 +9413,16 @@
     </row>
     <row r="153" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>79</v>
@@ -9433,16 +9433,16 @@
     </row>
     <row r="154" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>79</v>
@@ -9453,16 +9453,16 @@
     </row>
     <row r="155" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>79</v>
@@ -9473,16 +9473,16 @@
     </row>
     <row r="156" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>79</v>
@@ -9493,16 +9493,16 @@
     </row>
     <row r="157" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>79</v>
@@ -9513,16 +9513,16 @@
     </row>
     <row r="158" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>79</v>
@@ -9533,16 +9533,16 @@
     </row>
     <row r="159" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>79</v>
@@ -9553,16 +9553,16 @@
     </row>
     <row r="160" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>79</v>
@@ -9573,16 +9573,16 @@
     </row>
     <row r="161" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>79</v>
@@ -9593,16 +9593,16 @@
     </row>
     <row r="162" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>79</v>
@@ -9613,16 +9613,16 @@
     </row>
     <row r="163" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>79</v>
@@ -9633,16 +9633,16 @@
     </row>
     <row r="164" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>79</v>
@@ -9653,16 +9653,16 @@
     </row>
     <row r="165" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>79</v>
@@ -9676,13 +9676,13 @@
         <v>26</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>81</v>
@@ -9693,16 +9693,16 @@
     </row>
     <row r="167" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>81</v>
@@ -9713,16 +9713,16 @@
     </row>
     <row r="168" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>81</v>
@@ -9733,16 +9733,16 @@
     </row>
     <row r="169" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>81</v>
@@ -9753,16 +9753,16 @@
     </row>
     <row r="170" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E170" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="C170" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>81</v>
